--- a/Assets/Editor/ItemData/ItemDataBase.xlsx
+++ b/Assets/Editor/ItemData/ItemDataBase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Editor\ItemData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F79829C-CC13-4FD8-B68A-BA1A3599A140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7C1C7A-3C40-411B-BC58-A96B2D321965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D1BC800-391A-4C02-A163-EB869A935FC6}"/>
   </bookViews>
@@ -151,9 +151,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>빛나는 제철 사과</t>
-  </si>
-  <si>
     <t>Apple</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -193,6 +190,10 @@
   </si>
   <si>
     <t>IsPercent</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 익은 사과</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1213,10 +1214,10 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -1236,7 +1237,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>20001</v>
@@ -1245,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>99</v>
@@ -1254,7 +1255,7 @@
         <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -1433,10 +1434,10 @@
         <v>20008</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>20008</v>
@@ -1445,7 +1446,7 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9">
         <v>99</v>
@@ -1459,10 +1460,10 @@
         <v>20009</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
       </c>
       <c r="D10">
         <v>20009</v>
@@ -1471,7 +1472,7 @@
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>99</v>
@@ -1480,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
